--- a/data/golden/documents/GD-22_po_servers.xlsx
+++ b/data/golden/documents/GD-22_po_servers.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dell China</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
     </row>
